--- a/Aye_Noor_Product_Catalog.xlsx
+++ b/Aye_Noor_Product_Catalog.xlsx
@@ -1507,7 +1507,7 @@
         <v>Large decorative peony flower-shaped candle with detailed petals.</v>
       </c>
       <c r="O2" t="str">
-        <v/>
+        <v>/uploads/products/an-001-1792148472372.jpeg</v>
       </c>
     </row>
     <row r="3">
